--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.3-70B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.3-70B-Instruct/simple/total_votes_file.xlsx
@@ -430,13 +430,13 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2">
         <v>370</v>
       </c>
       <c r="E2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D3">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E3">
         <v>19</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>426</v>
